--- a/InputData/indst/SoCaOMSbRIC/Share of Capital and OM Spending by ISIC Code.xlsx
+++ b/InputData/indst/SoCaOMSbRIC/Share of Capital and OM Spending by ISIC Code.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CodeRepositories\eps-us\InputData\indst\SoCaOMSbRIC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33CFB0F9-7E70-45BC-BB47-28AD84C78620}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DABA530-C33B-4F73-A967-9FDE6D8AA718}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1725" yWindow="435" windowWidth="26295" windowHeight="16380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2535" yWindow="45" windowWidth="25665" windowHeight="16830" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="82">
   <si>
     <t>ISIC 97T98</t>
   </si>
@@ -68,12 +68,6 @@
     <t>ISIC 22</t>
   </si>
   <si>
-    <t>ISIC 23</t>
-  </si>
-  <si>
-    <t>ISIC 24</t>
-  </si>
-  <si>
     <t>ISIC 25</t>
   </si>
   <si>
@@ -95,9 +89,6 @@
     <t>ISIC 31T33</t>
   </si>
   <si>
-    <t>ISIC 35T39</t>
-  </si>
-  <si>
     <t>ISIC 41T43</t>
   </si>
   <si>
@@ -270,6 +261,27 @@
   </si>
   <si>
     <t>ISIC 06</t>
+  </si>
+  <si>
+    <t>ISIC 231</t>
+  </si>
+  <si>
+    <t>ISIC 239</t>
+  </si>
+  <si>
+    <t>ISIC 241</t>
+  </si>
+  <si>
+    <t>ISIC 242</t>
+  </si>
+  <si>
+    <t>ISIC 351</t>
+  </si>
+  <si>
+    <t>ISIC 352T353</t>
+  </si>
+  <si>
+    <t>ISIC 36T39</t>
   </si>
 </sst>
 </file>
@@ -782,15 +794,15 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C3" s="4"/>
       <c r="D3" s="4"/>
@@ -800,7 +812,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -810,22 +822,22 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B7" s="2" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B10" s="4" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="6"/>
@@ -835,7 +847,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -845,47 +857,47 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B14" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -907,27 +919,27 @@
   <sheetData>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B25" t="s">
+        <v>37</v>
+      </c>
+      <c r="C25" t="s">
+        <v>38</v>
+      </c>
+      <c r="D25" t="s">
+        <v>39</v>
+      </c>
+      <c r="E25" t="s">
         <v>40</v>
       </c>
-      <c r="C25" t="s">
+      <c r="F25" t="s">
         <v>41</v>
-      </c>
-      <c r="D25" t="s">
-        <v>42</v>
-      </c>
-      <c r="E25" t="s">
-        <v>43</v>
-      </c>
-      <c r="F25" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B26">
         <v>57</v>
@@ -947,7 +959,7 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B27">
         <v>19</v>
@@ -967,7 +979,7 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B28">
         <v>46</v>
@@ -987,7 +999,7 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B29">
         <v>11</v>
@@ -1007,7 +1019,7 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B30">
         <f>14+26</f>
@@ -1029,30 +1041,30 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B32" t="s">
+        <v>37</v>
+      </c>
+      <c r="C32" t="s">
+        <v>38</v>
+      </c>
+      <c r="D32" t="s">
+        <v>39</v>
+      </c>
+      <c r="E32" t="s">
         <v>40</v>
       </c>
-      <c r="C32" t="s">
+      <c r="F32" t="s">
         <v>41</v>
       </c>
-      <c r="D32" t="s">
+      <c r="H32" t="s">
         <v>42</v>
-      </c>
-      <c r="E32" t="s">
-        <v>43</v>
-      </c>
-      <c r="F32" t="s">
-        <v>44</v>
-      </c>
-      <c r="H32" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B33" s="3">
         <f>B26/SUM(B$26:B$30)</f>
@@ -1081,7 +1093,7 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B34" s="3">
         <f t="shared" ref="B34:F37" si="1">B27/SUM(B$26:B$30)</f>
@@ -1110,7 +1122,7 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B35" s="3">
         <f t="shared" si="1"/>
@@ -1139,7 +1151,7 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B36" s="3">
         <f t="shared" si="1"/>
@@ -1168,7 +1180,7 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B37" s="3">
         <f t="shared" si="1"/>
@@ -1197,20 +1209,20 @@
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B85" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B87">
         <f>6.03-3.19</f>
@@ -1219,7 +1231,7 @@
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B88">
         <f>2.89-1.63</f>
@@ -1228,7 +1240,7 @@
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B89">
         <f>8.92-4.82</f>
@@ -1237,12 +1249,12 @@
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B91">
         <v>0</v>
@@ -1250,7 +1262,7 @@
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B92">
         <f>19.3-11.6</f>
@@ -1259,7 +1271,7 @@
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B93">
         <f>13.8-11</f>
@@ -1268,17 +1280,17 @@
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B97">
         <f>B87/SUM(B$87:B$89)</f>
@@ -1287,7 +1299,7 @@
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B98">
         <f>B88/SUM(B$87:B$89)</f>
@@ -1296,7 +1308,7 @@
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B99">
         <f>B89/SUM(B$87:B$89)</f>
@@ -1305,12 +1317,12 @@
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B101">
         <f>B91/SUM(B$91:B$93)</f>
@@ -1319,7 +1331,7 @@
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B102">
         <f t="shared" ref="B102:B103" si="3">B92/SUM(B$91:B$93)</f>
@@ -1328,7 +1340,7 @@
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B103">
         <f t="shared" si="3"/>
@@ -1337,7 +1349,7 @@
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.25">
@@ -1346,7 +1358,7 @@
         <v>22600000</v>
       </c>
       <c r="B106" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.25">
@@ -1355,17 +1367,17 @@
         <v>23222760</v>
       </c>
       <c r="B107" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B110">
         <f>A$106/SUM($A$106:$A$107)*B101+A$107/SUM($A$106:$A$107)*B97</f>
@@ -1374,7 +1386,7 @@
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B111">
         <f t="shared" ref="B111:B112" si="4">A$106/SUM($A$106:$A$107)*B102+A$107/SUM($A$106:$A$107)*B98</f>
@@ -1383,7 +1395,7 @@
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B112">
         <f t="shared" si="4"/>
@@ -1411,25 +1423,28 @@
   <sheetPr>
     <tabColor theme="8" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:AM2"/>
+  <dimension ref="A1:AQ2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25.42578125" customWidth="1"/>
-    <col min="2" max="39" width="9.85546875" customWidth="1"/>
+    <col min="2" max="26" width="9.85546875" customWidth="1"/>
+    <col min="27" max="27" width="12.85546875" customWidth="1"/>
+    <col min="28" max="28" width="10.5703125" customWidth="1"/>
+    <col min="29" max="43" width="9.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B1" s="8" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="E1" s="8" t="s">
         <v>2</v>
@@ -1453,93 +1468,105 @@
         <v>8</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="N1" s="8" t="s">
         <v>9</v>
       </c>
       <c r="O1" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="P1" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q1" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="R1" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="S1" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="P1" s="8" t="s">
+      <c r="T1" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="Q1" s="8" t="s">
+      <c r="U1" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="R1" s="8" t="s">
+      <c r="V1" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="S1" s="8" t="s">
+      <c r="W1" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="T1" s="8" t="s">
+      <c r="X1" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="U1" s="8" t="s">
+      <c r="Y1" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="V1" s="8" t="s">
+      <c r="Z1" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="AA1" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="AB1" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="AC1" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="W1" s="8" t="s">
+      <c r="AD1" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="X1" s="8" t="s">
+      <c r="AE1" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="Y1" s="8" t="s">
+      <c r="AF1" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="Z1" s="8" t="s">
+      <c r="AG1" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="AA1" s="8" t="s">
+      <c r="AH1" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="AB1" s="8" t="s">
+      <c r="AI1" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="AC1" s="8" t="s">
+      <c r="AJ1" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="AD1" s="8" t="s">
+      <c r="AK1" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="AE1" s="8" t="s">
+      <c r="AL1" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="AF1" s="8" t="s">
+      <c r="AM1" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="AG1" s="8" t="s">
+      <c r="AN1" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="AH1" s="8" t="s">
+      <c r="AO1" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="AI1" s="8" t="s">
+      <c r="AP1" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="AJ1" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="AK1" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="AL1" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="AM1" s="8" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="AQ1" s="8" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -1596,14 +1623,14 @@
         <v>0</v>
       </c>
       <c r="T2">
+        <v>0</v>
+      </c>
+      <c r="U2">
+        <v>0</v>
+      </c>
+      <c r="V2">
         <v>0.5</v>
       </c>
-      <c r="U2">
-        <v>0</v>
-      </c>
-      <c r="V2">
-        <v>0</v>
-      </c>
       <c r="W2">
         <v>0</v>
       </c>
@@ -1611,20 +1638,20 @@
         <v>0</v>
       </c>
       <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+      <c r="AA2">
+        <v>0</v>
+      </c>
+      <c r="AB2">
+        <v>0</v>
+      </c>
+      <c r="AC2">
         <v>0.2</v>
       </c>
-      <c r="Z2">
-        <v>0</v>
-      </c>
-      <c r="AA2">
-        <v>0</v>
-      </c>
-      <c r="AB2">
-        <v>0</v>
-      </c>
-      <c r="AC2">
-        <v>0</v>
-      </c>
       <c r="AD2">
         <v>0</v>
       </c>
@@ -1638,21 +1665,33 @@
         <v>0</v>
       </c>
       <c r="AH2">
+        <v>0</v>
+      </c>
+      <c r="AI2">
+        <v>0</v>
+      </c>
+      <c r="AJ2">
+        <v>0</v>
+      </c>
+      <c r="AK2">
+        <v>0</v>
+      </c>
+      <c r="AL2">
         <v>0.3</v>
       </c>
-      <c r="AI2">
-        <v>0</v>
-      </c>
-      <c r="AJ2">
-        <v>0</v>
-      </c>
-      <c r="AK2">
-        <v>0</v>
-      </c>
-      <c r="AL2">
-        <v>0</v>
-      </c>
       <c r="AM2">
+        <v>0</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <v>0</v>
+      </c>
+      <c r="AP2">
+        <v>0</v>
+      </c>
+      <c r="AQ2">
         <v>0</v>
       </c>
     </row>

--- a/InputData/indst/SoCaOMSbRIC/Share of Capital and OM Spending by ISIC Code.xlsx
+++ b/InputData/indst/SoCaOMSbRIC/Share of Capital and OM Spending by ISIC Code.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26831"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CodeRepositories\eps-us\InputData\indst\SoCaOMSbRIC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DABA530-C33B-4F73-A967-9FDE6D8AA718}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DABA530-C33B-4F73-A967-9FDE6D8AA718}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2535" yWindow="45" windowWidth="25665" windowHeight="16830" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
     <sheet name="Industry EE" sheetId="4" r:id="rId3"/>
     <sheet name="SoCaOMSbRIC" sheetId="1" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -29,6 +29,9 @@
         <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -38,250 +41,250 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="82">
   <si>
+    <t>SoCaOMSbRIC Share of Capital and OM Spending by Recipient ISIC Code</t>
+  </si>
+  <si>
+    <t>Sources:</t>
+  </si>
+  <si>
+    <t>CCS Costs</t>
+  </si>
+  <si>
+    <t>Global CCS Institute</t>
+  </si>
+  <si>
+    <t>GLOBAL COSTS OF CARBON CAPTURE AND STORAGE</t>
+  </si>
+  <si>
+    <t>https://www.globalccsinstitute.com/archive/hub/publications/201688/global-ccs-cost-updatev4.pdf</t>
+  </si>
+  <si>
+    <t>Tables C and E</t>
+  </si>
+  <si>
+    <t>Industrial EE Costs</t>
+  </si>
+  <si>
+    <t>Heidi Garrett-Peltier</t>
+  </si>
+  <si>
+    <t>Green versus brown: Comparing the employment impacts of energy efficiency, renewable energy, and fossil fuels using an input-output model</t>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/science/article/abs/pii/S026499931630709X</t>
+  </si>
+  <si>
+    <t>Table 2</t>
+  </si>
+  <si>
+    <t>Notes:</t>
+  </si>
+  <si>
+    <t>We compared two data sources on costs for industrial CCS and industrial energy efficiency</t>
+  </si>
+  <si>
+    <t>and found that the breakdown between labor (construction), machinery, and other</t>
+  </si>
+  <si>
+    <t>business services is comparable across studies. We therefore use a single set of assumptions</t>
+  </si>
+  <si>
+    <t>to cover the allocation of capital and OM expensies for industry energy efficiency and CCS.</t>
+  </si>
+  <si>
+    <t>A different input variable governs the breakdown of revenues due to Process Emissions policies.</t>
+  </si>
+  <si>
+    <t>Shares by Industry</t>
+  </si>
+  <si>
+    <t>Iron and Steel</t>
+  </si>
+  <si>
+    <t>Cement</t>
+  </si>
+  <si>
+    <t>Nat Gas</t>
+  </si>
+  <si>
+    <t>Fertilizer</t>
+  </si>
+  <si>
+    <t>Biomass-to-ethanol</t>
+  </si>
+  <si>
+    <t>equipment</t>
+  </si>
+  <si>
+    <t>materials</t>
+  </si>
+  <si>
+    <t>labor</t>
+  </si>
+  <si>
+    <t>Eng/CM/HO/Fees</t>
+  </si>
+  <si>
+    <t>Contingencies</t>
+  </si>
+  <si>
+    <t>Average</t>
+  </si>
+  <si>
+    <t>Incremental O&amp;M</t>
+  </si>
+  <si>
+    <t>PCS1</t>
+  </si>
+  <si>
+    <t>VOM</t>
+  </si>
+  <si>
+    <t>material</t>
+  </si>
+  <si>
+    <t>FOM</t>
+  </si>
+  <si>
+    <t>Incremental O&amp;M %</t>
+  </si>
+  <si>
+    <t>Estimated FOM and VOM costs at 50% CF</t>
+  </si>
+  <si>
+    <t>Share OM Costs</t>
+  </si>
+  <si>
+    <t>Unit: %</t>
+  </si>
+  <si>
+    <t>ISIC 01T03</t>
+  </si>
+  <si>
+    <t>ISIC 05</t>
+  </si>
+  <si>
+    <t>ISIC 06</t>
+  </si>
+  <si>
+    <t>ISIC 07T08</t>
+  </si>
+  <si>
+    <t>ISIC 09</t>
+  </si>
+  <si>
+    <t>ISIC 10T12</t>
+  </si>
+  <si>
+    <t>ISIC 13T15</t>
+  </si>
+  <si>
+    <t>ISIC 16</t>
+  </si>
+  <si>
+    <t>ISIC 17T18</t>
+  </si>
+  <si>
+    <t>ISIC 19</t>
+  </si>
+  <si>
+    <t>ISIC 20</t>
+  </si>
+  <si>
+    <t>ISIC 21</t>
+  </si>
+  <si>
+    <t>ISIC 22</t>
+  </si>
+  <si>
+    <t>ISIC 231</t>
+  </si>
+  <si>
+    <t>ISIC 239</t>
+  </si>
+  <si>
+    <t>ISIC 241</t>
+  </si>
+  <si>
+    <t>ISIC 242</t>
+  </si>
+  <si>
+    <t>ISIC 25</t>
+  </si>
+  <si>
+    <t>ISIC 26</t>
+  </si>
+  <si>
+    <t>ISIC 27</t>
+  </si>
+  <si>
+    <t>ISIC 28</t>
+  </si>
+  <si>
+    <t>ISIC 29</t>
+  </si>
+  <si>
+    <t>ISIC 30</t>
+  </si>
+  <si>
+    <t>ISIC 31T33</t>
+  </si>
+  <si>
+    <t>ISIC 351</t>
+  </si>
+  <si>
+    <t>ISIC 352T353</t>
+  </si>
+  <si>
+    <t>ISIC 36T39</t>
+  </si>
+  <si>
+    <t>ISIC 41T43</t>
+  </si>
+  <si>
+    <t>ISIC 45T47</t>
+  </si>
+  <si>
+    <t>ISIC 49T53</t>
+  </si>
+  <si>
+    <t>ISIC 55T56</t>
+  </si>
+  <si>
+    <t>ISIC 58T60</t>
+  </si>
+  <si>
+    <t>ISIC 61</t>
+  </si>
+  <si>
+    <t>ISIC 62T63</t>
+  </si>
+  <si>
+    <t>ISIC 64T66</t>
+  </si>
+  <si>
+    <t>ISIC 68</t>
+  </si>
+  <si>
+    <t>ISIC 69T82</t>
+  </si>
+  <si>
+    <t>ISIC 84</t>
+  </si>
+  <si>
+    <t>ISIC 85</t>
+  </si>
+  <si>
+    <t>ISIC 86T88</t>
+  </si>
+  <si>
+    <t>ISIC 90T96</t>
+  </si>
+  <si>
     <t>ISIC 97T98</t>
   </si>
   <si>
-    <t>ISIC 01T03</t>
-  </si>
-  <si>
-    <t>ISIC 07T08</t>
-  </si>
-  <si>
-    <t>ISIC 09</t>
-  </si>
-  <si>
-    <t>ISIC 10T12</t>
-  </si>
-  <si>
-    <t>ISIC 13T15</t>
-  </si>
-  <si>
-    <t>ISIC 16</t>
-  </si>
-  <si>
-    <t>ISIC 17T18</t>
-  </si>
-  <si>
-    <t>ISIC 19</t>
-  </si>
-  <si>
-    <t>ISIC 22</t>
-  </si>
-  <si>
-    <t>ISIC 25</t>
-  </si>
-  <si>
-    <t>ISIC 26</t>
-  </si>
-  <si>
-    <t>ISIC 27</t>
-  </si>
-  <si>
-    <t>ISIC 28</t>
-  </si>
-  <si>
-    <t>ISIC 29</t>
-  </si>
-  <si>
-    <t>ISIC 30</t>
-  </si>
-  <si>
-    <t>ISIC 31T33</t>
-  </si>
-  <si>
-    <t>ISIC 41T43</t>
-  </si>
-  <si>
-    <t>ISIC 45T47</t>
-  </si>
-  <si>
-    <t>ISIC 49T53</t>
-  </si>
-  <si>
-    <t>ISIC 55T56</t>
-  </si>
-  <si>
-    <t>ISIC 58T60</t>
-  </si>
-  <si>
-    <t>ISIC 61</t>
-  </si>
-  <si>
-    <t>ISIC 62T63</t>
-  </si>
-  <si>
-    <t>ISIC 64T66</t>
-  </si>
-  <si>
-    <t>ISIC 68</t>
-  </si>
-  <si>
-    <t>ISIC 69T82</t>
-  </si>
-  <si>
-    <t>ISIC 84</t>
-  </si>
-  <si>
-    <t>ISIC 85</t>
-  </si>
-  <si>
-    <t>ISIC 86T88</t>
-  </si>
-  <si>
-    <t>ISIC 90T96</t>
-  </si>
-  <si>
-    <t>Shares by Industry</t>
-  </si>
-  <si>
-    <t>equipment</t>
-  </si>
-  <si>
-    <t>materials</t>
-  </si>
-  <si>
-    <t>labor</t>
-  </si>
-  <si>
-    <t>Eng/CM/HO/Fees</t>
-  </si>
-  <si>
-    <t>Contingencies</t>
-  </si>
-  <si>
-    <t>Iron and Steel</t>
-  </si>
-  <si>
-    <t>Cement</t>
-  </si>
-  <si>
-    <t>Nat Gas</t>
-  </si>
-  <si>
-    <t>Fertilizer</t>
-  </si>
-  <si>
-    <t>Biomass-to-ethanol</t>
-  </si>
-  <si>
-    <t>Average</t>
-  </si>
-  <si>
-    <t>https://www.globalccsinstitute.com/archive/hub/publications/201688/global-ccs-cost-updatev4.pdf</t>
-  </si>
-  <si>
-    <t>PCS1</t>
-  </si>
-  <si>
-    <t>Incremental O&amp;M</t>
-  </si>
-  <si>
-    <t>material</t>
-  </si>
-  <si>
-    <t>VOM</t>
-  </si>
-  <si>
-    <t>FOM</t>
-  </si>
-  <si>
-    <t>Incremental O&amp;M %</t>
-  </si>
-  <si>
-    <t>Estimated FOM and VOM costs at 50% CF</t>
-  </si>
-  <si>
-    <t>Share OM Costs</t>
-  </si>
-  <si>
-    <t>https://www.sciencedirect.com/science/article/abs/pii/S026499931630709X</t>
-  </si>
-  <si>
     <t>Share of Costs by ISIC Code</t>
-  </si>
-  <si>
-    <t>CCS Costs</t>
-  </si>
-  <si>
-    <t>Industrial EE Costs</t>
-  </si>
-  <si>
-    <t>Sources:</t>
-  </si>
-  <si>
-    <t>Global CCS Institute</t>
-  </si>
-  <si>
-    <t>GLOBAL COSTS OF CARBON CAPTURE AND STORAGE</t>
-  </si>
-  <si>
-    <t>Tables C and E</t>
-  </si>
-  <si>
-    <t>Heidi Garrett-Peltier</t>
-  </si>
-  <si>
-    <t>Green versus brown: Comparing the employment impacts of energy efficiency, renewable energy, and fossil fuels using an input-output model</t>
-  </si>
-  <si>
-    <t>Table 2</t>
-  </si>
-  <si>
-    <t>Notes:</t>
-  </si>
-  <si>
-    <t>We compared two data sources on costs for industrial CCS and industrial energy efficiency</t>
-  </si>
-  <si>
-    <t>and found that the breakdown between labor (construction), machinery, and other</t>
-  </si>
-  <si>
-    <t>business services is comparable across studies. We therefore use a single set of assumptions</t>
-  </si>
-  <si>
-    <t>Unit: %</t>
-  </si>
-  <si>
-    <t>SoCaOMSbRIC Share of Capital and OM Spending by Recipient ISIC Code</t>
-  </si>
-  <si>
-    <t>to cover the allocation of capital and OM expensies for industry energy efficiency and CCS.</t>
-  </si>
-  <si>
-    <t>A different input variable governs the breakdown of revenues due to Process Emissions policies.</t>
-  </si>
-  <si>
-    <t>ISIC 20</t>
-  </si>
-  <si>
-    <t>ISIC 21</t>
-  </si>
-  <si>
-    <t>ISIC 05</t>
-  </si>
-  <si>
-    <t>ISIC 06</t>
-  </si>
-  <si>
-    <t>ISIC 231</t>
-  </si>
-  <si>
-    <t>ISIC 239</t>
-  </si>
-  <si>
-    <t>ISIC 241</t>
-  </si>
-  <si>
-    <t>ISIC 242</t>
-  </si>
-  <si>
-    <t>ISIC 351</t>
-  </si>
-  <si>
-    <t>ISIC 352T353</t>
-  </si>
-  <si>
-    <t>ISIC 36T39</t>
   </si>
 </sst>
 </file>
@@ -291,7 +294,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -351,7 +354,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2"/>
@@ -361,7 +364,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -790,19 +792,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G23"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
       <c r="A3" s="1" t="s">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>54</v>
+        <v>2</v>
       </c>
       <c r="C3" s="4"/>
       <c r="D3" s="4"/>
@@ -810,34 +812,34 @@
       <c r="F3" s="6"/>
       <c r="G3" s="6"/>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7">
       <c r="B4" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
       <c r="B5" s="5">
         <v>2017</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7">
       <c r="B6" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
       <c r="B7" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
       <c r="B8" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
       <c r="B10" s="4" t="s">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="6"/>
@@ -845,59 +847,59 @@
       <c r="F10" s="6"/>
       <c r="G10" s="6"/>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7">
       <c r="B11" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
       <c r="B12" s="5">
         <v>2017</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7">
       <c r="B13" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
       <c r="B14" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
       <c r="B15" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="7" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>70</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -912,34 +914,34 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A25:H112"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="17.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8">
       <c r="A25" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="B25" t="s">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="C25" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="D25" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="E25" t="s">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="F25" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
       <c r="A26" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="B26">
         <v>57</v>
@@ -957,9 +959,9 @@
         <v>22</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8">
       <c r="A27" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="B27">
         <v>19</v>
@@ -977,9 +979,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8">
       <c r="A28" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="B28">
         <v>46</v>
@@ -997,9 +999,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8">
       <c r="A29" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="B29">
         <v>11</v>
@@ -1017,9 +1019,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8">
       <c r="A30" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="B30">
         <f>14+26</f>
@@ -1039,32 +1041,32 @@
         <v>8</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8">
       <c r="A32" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="B32" t="s">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="C32" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="D32" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="E32" t="s">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="F32" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="H32" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8">
       <c r="A33" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="B33" s="3">
         <f>B26/SUM(B$26:B$30)</f>
@@ -1091,9 +1093,9 @@
         <v>0.40358302858715744</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8">
       <c r="A34" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="B34" s="3">
         <f t="shared" ref="B34:F37" si="1">B27/SUM(B$26:B$30)</f>
@@ -1120,9 +1122,9 @@
         <v>9.0808855334041122E-2</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8">
       <c r="A35" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="B35" s="3">
         <f t="shared" si="1"/>
@@ -1149,9 +1151,9 @@
         <v>0.24964177578545868</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8">
       <c r="A36" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="B36" s="3">
         <f t="shared" si="1"/>
@@ -1178,9 +1180,9 @@
         <v>7.2036490896936797E-2</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8">
       <c r="A37" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="B37" s="3">
         <f t="shared" si="1"/>
@@ -1207,195 +1209,195 @@
         <v>0.18392984939640594</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:2">
       <c r="A85" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="B85" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2">
       <c r="A86" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2">
       <c r="A87" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="B87">
         <f>6.03-3.19</f>
         <v>2.8400000000000003</v>
       </c>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:2">
       <c r="A88" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="B88">
         <f>2.89-1.63</f>
         <v>1.2600000000000002</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:2">
       <c r="A89" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="B89">
         <f>8.92-4.82</f>
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:2">
       <c r="A90" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2">
       <c r="A91" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="B91">
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:2">
       <c r="A92" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="B92">
         <f>19.3-11.6</f>
         <v>7.7000000000000011</v>
       </c>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:2">
       <c r="A93" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="B93">
         <f>13.8-11</f>
         <v>2.8000000000000007</v>
       </c>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:2">
       <c r="A95" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2">
       <c r="A96" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2">
       <c r="A97" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="B97">
         <f>B87/SUM(B$87:B$89)</f>
         <v>0.34634146341463423</v>
       </c>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:2">
       <c r="A98" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="B98">
         <f>B88/SUM(B$87:B$89)</f>
         <v>0.15365853658536591</v>
       </c>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:2">
       <c r="A99" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="B99">
         <f>B89/SUM(B$87:B$89)</f>
         <v>0.5</v>
       </c>
     </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:2">
       <c r="A100" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2">
       <c r="A101" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="B101">
         <f>B91/SUM(B$91:B$93)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:2">
       <c r="A102" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="B102">
         <f t="shared" ref="B102:B103" si="3">B92/SUM(B$91:B$93)</f>
         <v>0.73333333333333328</v>
       </c>
     </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:2">
       <c r="A103" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="B103">
         <f t="shared" si="3"/>
         <v>0.26666666666666666</v>
       </c>
     </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:2">
       <c r="A105" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2">
       <c r="A106">
         <f>22600000</f>
         <v>22600000</v>
       </c>
       <c r="B106" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2">
       <c r="A107">
         <f>9.64*550*8760*0.5</f>
         <v>23222760</v>
       </c>
       <c r="B107" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2">
       <c r="A109" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2">
       <c r="A110" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="B110">
         <f>A$106/SUM($A$106:$A$107)*B101+A$107/SUM($A$106:$A$107)*B97</f>
         <v>0.17552423038085946</v>
       </c>
     </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:2">
       <c r="A111" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="B111">
         <f t="shared" ref="B111:B112" si="4">A$106/SUM($A$106:$A$107)*B102+A$107/SUM($A$106:$A$107)*B98</f>
         <v>0.43955686323579163</v>
       </c>
     </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:2">
       <c r="A112" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="B112">
         <f t="shared" si="4"/>
@@ -1411,7 +1413,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -1424,7 +1426,7 @@
     <tabColor theme="8" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:AQ2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.42578125" customWidth="1"/>
     <col min="2" max="26" width="9.85546875" customWidth="1"/>
@@ -1433,140 +1435,140 @@
     <col min="29" max="43" width="9.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:43">
       <c r="A1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="K1" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="L1" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="M1" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="N1" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="O1" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="P1" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q1" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="R1" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="S1" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="T1" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="U1" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="V1" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="W1" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="X1" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="Y1" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="Z1" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="AA1" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="AB1" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="AC1" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="AD1" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="8" t="s">
+      <c r="AE1" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="AF1" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="AG1" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="AH1" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="AI1" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="AJ1" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="AK1" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="E1" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="J1" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="K1" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="L1" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="M1" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="N1" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="O1" s="8" t="s">
+      <c r="AL1" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="P1" s="8" t="s">
+      <c r="AM1" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="Q1" s="8" t="s">
+      <c r="AN1" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="R1" s="8" t="s">
+      <c r="AO1" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="S1" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="T1" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="U1" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="V1" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="W1" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="X1" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="Y1" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="Z1" s="8" t="s">
+      <c r="AP1" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="AA1" s="8" t="s">
+      <c r="AQ1" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="AB1" s="8" t="s">
+    </row>
+    <row r="2" spans="1:43">
+      <c r="A2" t="s">
         <v>81</v>
-      </c>
-      <c r="AC1" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="AD1" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="AE1" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="AF1" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="AG1" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="AH1" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="AI1" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="AJ1" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="AK1" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="AL1" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="AM1" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="AN1" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="AO1" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="AP1" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="AQ1" s="8" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>53</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -1698,4 +1700,169 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A251C7805F896F47A4F48569C73A0799" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="378e06851fdbb175a3d0a15b25cca813">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f3083de3-5d4e-49f2-a3cd-0aeb079e6739" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1ff5ef3c1d0a8a18c2d988b302a3fc15" ns2:_="">
+    <xsd:import namespace="f3083de3-5d4e-49f2-a3cd-0aeb079e6739"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="f3083de3-5d4e-49f2-a3cd-0aeb079e6739" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="10" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{80C3A5E5-22E9-4BC3-8713-BA8BE4F889AC}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{672082AD-70D7-4552-BF93-19B4EB050C7C}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{876D3E35-7D43-4A2C-A0BD-43935E53D211}"/>
 </file>